--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260728.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.86%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.28%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>45,654,000</t>
+          <t>46,121,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -721,100 +721,100 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>33,959,000</t>
+          <t>34,303,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>9,544,000</t>
+          <t>20,517,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>20,339,000</t>
+          <t>3,801,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,801,000</t>
+          <t>9,544,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11,037,000</t>
+          <t>24,881,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.70%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>6,485,000</t>
+          <t>11,037,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>24,881,000</t>
+          <t>6,485,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -924,68 +924,68 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,820,000</t>
+          <t>2,151,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>4,126,000</t>
+          <t>9,415,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>8,977,000</t>
+          <t>33,782,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>15,056,000</t>
+          <t>4,126,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,151,000</t>
+          <t>2,820,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,22 +1063,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>32,659,000</t>
+          <t>15,056,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -1100,46 +1100,46 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>3,862,000</t>
+          <t>8,904,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2,619,035,808</t>
+          <t>3,862,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,66 +1151,66 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>14,134,000</t>
+          <t>2,498,166,473</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>40,734,000</t>
+          <t>14,134,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>8,904,000</t>
+          <t>40,734,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>5,983,000</t>
+          <t>6,220,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1371,66 +1371,66 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>16,505,000</t>
+          <t>23,205,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>23,205,000</t>
+          <t>1,925,945,322</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2,002,785,322</t>
+          <t>16,505,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,870,000</t>
+          <t>7,223,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1591,83 +1591,83 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>8,865,000</t>
+          <t>47,231,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>47,231,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>6,330,000</t>
+          <t>48,929,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>48,929,000</t>
+          <t>6,330,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>17,290,000</t>
+          <t>16,588,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,44 +1701,44 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>16,588,000</t>
+          <t>17,282,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>16,216,000</t>
+          <t>17,290,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-50,087,598</t>
+          <t>-97,517,925</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
     </row>
